--- a/public/data/contract_payment_plan.xlsx
+++ b/public/data/contract_payment_plan.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>789578cf-d5f9-411e-882e-405dea514d4b</v>
+        <v>b676824d-8088-46b1-af0e-3dabeda92892</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0debe503-caf2-489f-8e7b-201b07b12168</v>
+        <v>4d803241-4d32-4c71-8099-5c23ac12d9ec</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -470,85 +470,85 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>8f801705-4624-4d60-b2a9-f73cd9e592bc</v>
+        <v>dd23ce50-4507-4d7d-9e53-ff2a816d976d</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
         <v>Payment terms</v>
       </c>
       <c r="F4" t="str">
-        <v>Net 30 days</v>
+        <v>Net 15 days</v>
       </c>
       <c r="G4" t="str">
-        <v>Monthly billing</v>
+        <v>Charter prepayment</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>b16c3d62-cda2-4b14-a2a1-423b7eecb8b9</v>
+        <v>9666c103-5af5-40de-9704-e87aea932cfc</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E5" t="str">
         <v>Payment terms</v>
       </c>
       <c r="F5" t="str">
-        <v>Net 15 days</v>
+        <v>Net 30 days</v>
       </c>
       <c r="G5" t="str">
-        <v>Charter prepayment required</v>
+        <v>Monthly billing</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>a9a13239-2a31-433e-a172-02f801b3ce71</v>
+        <v>46eb0685-1f5a-4ade-9bac-cd0e61d78ef9</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E6" t="str">
         <v>Payment terms</v>
       </c>
       <c r="F6" t="str">
-        <v>Net 30 days</v>
+        <v>Net 15 days</v>
       </c>
       <c r="G6" t="str">
-        <v>Standard Marriott terms</v>
+        <v>Charter prepayment required</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>94ff415c-c124-4d07-8a49-9a2cf1e1f175</v>
+        <v>fceb5e73-0b09-4222-bd58-312f9cca3645</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E7" t="str">
         <v>Payment terms</v>
@@ -557,159 +557,159 @@
         <v>Net 30 days</v>
       </c>
       <c r="G7" t="str">
-        <v>Monthly invoice to FS finance</v>
+        <v>Monthly billing</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>16e36757-9df1-45c0-9ff9-e8894aadfa6d</v>
+        <v>e60fd999-b159-41a1-be93-c6fca5b93c6b</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E8" t="str">
-        <v>Payment method</v>
+        <v>Payment terms</v>
       </c>
       <c r="F8" t="str">
-        <v>Bank transfer / Wire</v>
+        <v>Prepaid</v>
       </c>
       <c r="G8" t="str">
-        <v>USD or EUR accepted</v>
+        <v>Full payment before flight</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>dd927ef1-ad0d-4d29-8620-3e74f9149ac2</v>
+        <v>bfb49c5d-791c-49dd-bf91-edce1b8cdd5b</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E9" t="str">
-        <v>Late payment</v>
+        <v>Payment terms</v>
       </c>
       <c r="F9" t="str">
-        <v>1.5% per month</v>
+        <v>Net 30 days</v>
       </c>
       <c r="G9" t="str">
-        <v>Applied after 45 days</v>
+        <v>Standard Marriott terms</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>82008e57-c567-4cdf-8efc-434cc192e54c</v>
+        <v>b4e1fc0f-7855-41b4-8430-800dcc69902a</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E10" t="str">
         <v>Payment terms</v>
       </c>
       <c r="F10" t="str">
-        <v>Net 30 days</v>
+        <v>Net 15 days</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>Charter prepayment</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ab1f4266-56de-4272-a0e3-fcac4cb82028</v>
+        <v>4fe42f39-a036-4e5f-990f-6a4842dbb60b</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E11" t="str">
         <v>Payment terms</v>
       </c>
       <c r="F11" t="str">
-        <v>Net 15 days</v>
+        <v>Net 30 days</v>
       </c>
       <c r="G11" t="str">
-        <v>Charter prepayment</v>
+        <v>Monthly invoice to FS finance</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ed2a7b31-525d-4e19-9ed1-09bd9b2280d6</v>
+        <v>e520c10a-e14c-4d6d-b21f-e7fd8ae63ee2</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E12" t="str">
-        <v>Deposit</v>
+        <v>Payment method</v>
       </c>
       <c r="F12" t="str">
-        <v>20% upfront</v>
+        <v>Bank transfer / Wire</v>
       </c>
       <c r="G12" t="str">
-        <v>Balance on monthly invoice</v>
+        <v>USD or EUR accepted</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>496126e1-5152-4fe9-bd2d-4ee02155c2d5</v>
+        <v>e2eb41f9-e483-4151-afb0-bf1a61b6c72b</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E13" t="str">
-        <v>Payment terms</v>
+        <v>Late payment</v>
       </c>
       <c r="F13" t="str">
-        <v>Net 30 days</v>
+        <v>1.5% per month</v>
       </c>
       <c r="G13" t="str">
-        <v>Marriott centralized billing</v>
+        <v>Applied after 45 days</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>f9515983-19b7-4a9c-9388-4d713b3b4557</v>
+        <v>63abc6e2-2bf4-4389-8d0c-a96753b99614</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
-        <v>CTR-010-001</v>
+        <v>CTR-006-002</v>
       </c>
       <c r="E14" t="str">
         <v>Payment terms</v>
@@ -718,12 +718,219 @@
         <v>Net 15 days</v>
       </c>
       <c r="G14" t="str">
+        <v>Charter invoice</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>35ce2e24-eaeb-4701-983b-5872f1f56751</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Payment terms</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Prepaid</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Full payment 48h before</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>d64d714a-eeb7-4c20-b010-83e20c744247</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Payment terms</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Net 30 days</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3b8746a6-bf61-4b65-89cc-7395004106b8</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Payment terms</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Net 30 days</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>a9a4e993-fb0b-496e-8918-901d319e8b82</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Payment terms</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Net 15 days</v>
+      </c>
+      <c r="G18" t="str">
         <v>Charter prepayment</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>6fc7e2e6-b5fa-4579-8ff2-13d057ec289b</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Deposit</v>
+      </c>
+      <c r="F19" t="str">
+        <v>20% upfront</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Balance on monthly invoice</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>c50e10ae-4096-4bc3-a921-1a8826b4a87c</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Payment terms</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Net 30 days</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Standard transfer billing</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>69c52de7-2e11-43bf-a587-c3168d02d71a</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Payment terms</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Net 30 days</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Marriott centralized billing</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>a69666fd-f899-41cf-b62b-8d0d962457b7</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CTR-010-001</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Payment terms</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Net 15 days</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Charter prepayment</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>1bc68fbf-a433-40d8-9ddb-dc8163402458</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D23" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Payment terms</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Net 30 days</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Monthly billing</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G23"/>
   </ignoredErrors>
 </worksheet>
 </file>